--- a/用户导入测试.xlsx
+++ b/用户导入测试.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8460"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
   <si>
     <t>EHR号</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>组别</t>
+  </si>
+  <si>
+    <t>角色</t>
   </si>
   <si>
     <t>密码</t>
@@ -49,10 +52,19 @@
     <t>测试组</t>
   </si>
   <si>
+    <t>普通用户</t>
+  </si>
+  <si>
     <t>测试4</t>
   </si>
   <si>
     <t>测试5</t>
+  </si>
+  <si>
+    <t>测试7</t>
+  </si>
+  <si>
+    <t>测试8</t>
   </si>
 </sst>
 </file>
@@ -983,10 +995,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -999,46 +1011,92 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1234569</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2">
         <v>1234567</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1234566</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3">
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3">
         <v>1234567</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1234565</v>
       </c>
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
+      <c r="E4">
+        <v>1234567</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>1234567</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>1234567</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>1234568</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6">
         <v>1234567</v>
       </c>
     </row>

--- a/用户导入测试.xlsx
+++ b/用户导入测试.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="29400" windowHeight="12400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
   <si>
     <t>EHR号</t>
   </si>
@@ -49,13 +49,16 @@
     <t>测试3</t>
   </si>
   <si>
+    <t>娱乐组</t>
+  </si>
+  <si>
+    <t>普通用户</t>
+  </si>
+  <si>
+    <t>测试4</t>
+  </si>
+  <si>
     <t>测试组</t>
-  </si>
-  <si>
-    <t>普通用户</t>
-  </si>
-  <si>
-    <t>测试4</t>
   </si>
   <si>
     <t>测试5</t>
@@ -996,7 +999,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1040,7 +1043,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -1054,10 +1057,10 @@
         <v>1234565</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -1071,10 +1074,10 @@
         <v>1234567</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -1088,10 +1091,10 @@
         <v>1234568</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -1111,7 +1114,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1123,7 +1126,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
